--- a/data/Revenue & Profit Margin by Product.xlsx
+++ b/data/Revenue & Profit Margin by Product.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,49 +446,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Class 1 Milk</t>
+          <t>Class 1 milk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ice Cream</t>
+          <t>Whipping Cream</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Soft Serve Mix</t>
+          <t>Ice Cream Mix</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sour Cream</t>
+          <t>Soft Serve Mix</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chip Dip</t>
+          <t>Butter</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Sour Cream &amp; Chip Dip</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other (eggnog, co-packed)</t>
         </is>
       </c>
     </row>

--- a/data/Revenue & Profit Margin by Product.xlsx
+++ b/data/Revenue & Profit Margin by Product.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -453,59 +453,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Whipping Cream</t>
+          <t>Ice Cream</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ice Cream Mix</t>
+          <t>Soft Serve Mix</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Soft Serve Mix</t>
+          <t>Butter</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Sour Cream &amp; Chip Dip</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sour Cream &amp; Chip Dip</t>
+          <t>Other (eggnog, co-packed)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Other (eggnog, co-packed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>Overall Profit Margin (weighted avg)</t>
         </is>
       </c>
-      <c r="C9">
-        <f>SUMPRODUCT(B2:B8</f>
+      <c r="C8">
+        <f>IFERROR(SUMPRODUCT(B2:B7,C2:C7)/SUM(B2:B7),0)</f>
         <v/>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>C2:C8)/SUM(B2:B8)</t>
-        </is>
       </c>
     </row>
   </sheetData>
